--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_individual_h_2.xlsx
@@ -658,7 +658,7 @@
         <v>0.008407015632763826</v>
       </c>
       <c r="C2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9782765</v>
+        <v>4824430</v>
       </c>
       <c r="L2" t="n">
-        <v>6056433</v>
+        <v>2904669</v>
       </c>
       <c r="M2" t="n">
-        <v>1498768</v>
+        <v>708991</v>
       </c>
       <c r="N2" t="n">
-        <v>60127</v>
+        <v>23805</v>
       </c>
       <c r="O2" t="n">
-        <v>842487</v>
+        <v>400578</v>
       </c>
       <c r="P2" t="n">
-        <v>317055</v>
+        <v>148385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999916553497314</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.958172619342804</v>
+        <v>0.9363389015197754</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8975005149841309</v>
+        <v>0.869678795337677</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8775527477264404</v>
+        <v>0.8298290371894836</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2940468788146973</v>
+        <v>0.2467095106840134</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8951809406280518</v>
+        <v>0.8526328802108765</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9675278067588806</v>
+        <v>0.9479107260704041</v>
       </c>
       <c r="X2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12692760</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567423462867737</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911146342754364</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582749962806702</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6627725958824158</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020447134971619</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -792,130 +792,130 @@
         <v>0.002014765064493864</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9782765</v>
+        <v>4824430</v>
       </c>
       <c r="E3" t="n">
-        <v>358471</v>
+        <v>243591</v>
       </c>
       <c r="F3" t="n">
-        <v>1770</v>
+        <v>1031</v>
       </c>
       <c r="G3" t="n">
-        <v>335</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>20139134</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>22261534</v>
+        <v>11018683</v>
       </c>
       <c r="L3" t="n">
-        <v>25594524</v>
+        <v>12705873</v>
       </c>
       <c r="M3" t="n">
-        <v>30756008</v>
+        <v>15336899</v>
       </c>
       <c r="N3" t="n">
-        <v>32509192</v>
+        <v>16254050</v>
       </c>
       <c r="O3" t="n">
-        <v>31715189</v>
+        <v>15837572</v>
       </c>
       <c r="P3" t="n">
-        <v>32434814</v>
+        <v>16214564</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9644448161125183</v>
+        <v>0.9516941905021667</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9252398014068604</v>
+        <v>0.8869589567184448</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8028261065483093</v>
+        <v>0.7593267560005188</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3369327783584595</v>
+        <v>0.2666778564453125</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8274586796760559</v>
+        <v>0.7866919040679932</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8202279210090637</v>
+        <v>0.7677124738693237</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9714356</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>398208</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17110</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13592</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20139240</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22249364</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25705317</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30700729</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32593417</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31714153</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32418947</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9577006697654724</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099981188774109</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85770583152771</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622154712677002</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015981554985046</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>390456</v>
+        <v>301249</v>
       </c>
       <c r="E4" t="n">
-        <v>6056433</v>
+        <v>2904669</v>
       </c>
       <c r="F4" t="n">
-        <v>97205</v>
+        <v>67532</v>
       </c>
       <c r="G4" t="n">
-        <v>1043</v>
+        <v>784</v>
       </c>
       <c r="H4" t="n">
-        <v>626</v>
+        <v>602</v>
       </c>
       <c r="I4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>427050</v>
+        <v>328010</v>
       </c>
       <c r="L4" t="n">
-        <v>691678</v>
+        <v>435264</v>
       </c>
       <c r="M4" t="n">
-        <v>209127</v>
+        <v>145391</v>
       </c>
       <c r="N4" t="n">
-        <v>144354</v>
+        <v>72685</v>
       </c>
       <c r="O4" t="n">
-        <v>98649</v>
+        <v>69235</v>
       </c>
       <c r="P4" t="n">
-        <v>10641</v>
+        <v>8154</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999958276748657</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9612985253334045</v>
+        <v>0.9439540505409241</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9111590981483459</v>
+        <v>0.8782338500022888</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8385278582572937</v>
+        <v>0.7930139899253845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3140324056148529</v>
+        <v>0.2563053369522095</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8599886298179626</v>
+        <v>0.8183361887931824</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8878095746040344</v>
+        <v>0.8483482003211975</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>410116</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5956664</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>165604</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>10994</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>439220</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>580885</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>264406</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60129</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99685</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572212696075439</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9105718731880188</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579903244972229</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.662493884563446</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018213748931885</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,127 +1059,127 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>25249</v>
+        <v>17588</v>
       </c>
       <c r="E5" t="n">
-        <v>289757</v>
+        <v>171758</v>
       </c>
       <c r="F5" t="n">
-        <v>1498768</v>
+        <v>708991</v>
       </c>
       <c r="G5" t="n">
-        <v>32430</v>
+        <v>15492</v>
       </c>
       <c r="H5" t="n">
-        <v>20223</v>
+        <v>19463</v>
       </c>
       <c r="I5" t="n">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>360651</v>
+        <v>244877</v>
       </c>
       <c r="L5" t="n">
-        <v>489365</v>
+        <v>370194</v>
       </c>
       <c r="M5" t="n">
-        <v>368097</v>
+        <v>224719</v>
       </c>
       <c r="N5" t="n">
-        <v>118327</v>
+        <v>65460</v>
       </c>
       <c r="O5" t="n">
-        <v>175675</v>
+        <v>108615</v>
       </c>
       <c r="P5" t="n">
-        <v>69490</v>
+        <v>44897</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999967813491821</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9760081171989441</v>
+        <v>0.9651018977165222</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9640277028083801</v>
+        <v>0.9509345889091492</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9824188351631165</v>
+        <v>0.9774543046951294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919992089271545</v>
+        <v>0.9915847182273865</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9916446208953857</v>
+        <v>0.9891660809516907</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9975593686103821</v>
+        <v>0.9967683553695679</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16069</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170194</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1601221</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19877</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58238</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>429060</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>589134</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>265644</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60279</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100189</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735538363456726</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643634557723999</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983855664730072</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996332585811615</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939122200012207</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983846545219421</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
@@ -1189,22 +1189,22 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>11317</v>
+        <v>9148</v>
       </c>
       <c r="E6" t="n">
-        <v>42245</v>
+        <v>18727</v>
       </c>
       <c r="F6" t="n">
-        <v>54193</v>
+        <v>31706</v>
       </c>
       <c r="G6" t="n">
-        <v>60127</v>
+        <v>23805</v>
       </c>
       <c r="H6" t="n">
-        <v>10234</v>
+        <v>5725</v>
       </c>
       <c r="I6" t="n">
-        <v>334</v>
+        <v>150</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12924</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10697</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21742</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118175</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13954</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>1098</v>
+        <v>1090</v>
       </c>
       <c r="F7" t="n">
-        <v>55444</v>
+        <v>44669</v>
       </c>
       <c r="G7" t="n">
-        <v>109289</v>
+        <v>55288</v>
       </c>
       <c r="H7" t="n">
-        <v>842487</v>
+        <v>400578</v>
       </c>
       <c r="I7" t="n">
-        <v>9830</v>
+        <v>7557</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59290</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15136</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>917973</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="F8" t="n">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c r="G8" t="n">
-        <v>1257</v>
+        <v>903</v>
       </c>
       <c r="H8" t="n">
-        <v>67500</v>
+        <v>43413</v>
       </c>
       <c r="I8" t="n">
-        <v>317055</v>
+        <v>148385</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
